--- a/stories/arbres/TREE-SEC-041.xlsx
+++ b/stories/arbres/TREE-SEC-041.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Léa est avec maman, dans le jardin. Léa a envie de jouer. maman est là, tout près. On va apprendre : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa écoute maman. Léa entend les mots : appeler un adulte, mains avec les jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -2005,6 +2043,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2357,6 +2405,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2598,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2713,6 +2771,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2938,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3109,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3276,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3447,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3614,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3785,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3885,6 +3978,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4053,6 +4151,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4215,6 +4318,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4381,6 +4489,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4543,6 +4656,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4709,6 +4827,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4871,6 +4994,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5037,6 +5165,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5225,6 +5358,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5393,6 +5531,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5555,6 +5698,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5721,6 +5869,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5883,6 +6036,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6049,6 +6207,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6211,6 +6374,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6235,7 +6403,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6377,6 +6545,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6557,6 +6731,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -6729,6 +6908,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6915,6 +7099,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7081,6 +7270,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7269,6 +7463,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7437,6 +7636,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7599,6 +7803,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7765,6 +7974,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7927,6 +8141,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8093,6 +8312,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8255,6 +8479,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8421,6 +8650,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8609,6 +8843,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8777,6 +9016,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8939,6 +9183,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9105,6 +9354,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9267,6 +9521,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9433,6 +9692,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9595,6 +9859,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9761,6 +10030,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9949,6 +10223,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10117,6 +10396,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10279,6 +10563,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10445,6 +10734,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10607,6 +10901,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10773,6 +11072,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10935,6 +11239,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10959,7 +11268,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tient la main. maman dit : je suis là. On reste ensemble.</t>
+          <t>Léa va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11101,6 +11410,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Léa se souvient : appeler un adulte, mains avec les jouets. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. On se tient la main.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11281,6 +11596,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
     </row>
@@ -11453,6 +11773,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11639,6 +11964,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11805,6 +12135,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11993,6 +12328,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12161,6 +12501,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12323,6 +12668,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12489,6 +12839,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12651,6 +13006,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12817,6 +13177,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12979,6 +13344,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13145,6 +13515,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13333,6 +13708,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13501,6 +13881,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13663,6 +14048,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13829,6 +14219,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13991,6 +14386,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14157,6 +14557,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14319,6 +14724,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14485,6 +14895,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14673,6 +15088,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14841,6 +15261,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15003,6 +15428,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15169,6 +15599,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15331,6 +15766,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15497,6 +15937,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15659,6 +16104,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15677,7 +16127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15750,6 +16200,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-041.xlsx
+++ b/stories/arbres/TREE-SEC-041.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Léa est avec maman, dans le jardin. Léa a envie de jouer. maman est là, tout près. On va apprendre : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa écoute maman. Léa entend les mots : appeler un adulte, mains avec les jouets.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2048,6 +2057,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2410,6 +2421,7 @@
           <t>narrateur|Léa a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2605,6 +2617,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2776,6 +2789,7 @@
           <t>narrateur|Léa rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2943,6 +2957,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3114,6 +3129,7 @@
           <t>narrateur|Léa rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3281,6 +3297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3452,6 +3469,7 @@
           <t>narrateur|Léa rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le bac à sable, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3619,6 +3637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3790,6 +3809,7 @@
           <t>narrateur|Léa a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3985,6 +4005,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4156,6 +4177,7 @@
           <t>narrateur|Léa rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4323,6 +4345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4494,6 +4517,7 @@
           <t>narrateur|Léa rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4661,6 +4685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4832,6 +4857,7 @@
           <t>narrateur|Léa rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de le bac à sable, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4999,6 +5025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5170,6 +5197,7 @@
           <t>narrateur|Léa a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5365,6 +5393,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5536,6 +5565,7 @@
           <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5703,6 +5733,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5874,6 +5905,7 @@
           <t>narrateur|Léa rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6041,6 +6073,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6212,6 +6245,7 @@
           <t>narrateur|Léa rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de le bac à sable, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6379,6 +6413,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6551,6 +6586,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6738,6 +6774,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6913,6 +6950,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7104,6 +7142,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7275,6 +7314,7 @@
           <t>narrateur|Léa a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7470,6 +7510,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7641,6 +7682,7 @@
           <t>narrateur|Léa rejoint Tom. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7808,6 +7850,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7979,6 +8022,7 @@
           <t>narrateur|Léa rejoint Léa. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8146,6 +8190,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8317,6 +8362,7 @@
           <t>narrateur|Léa rejoint Sami. La couverture est douce. On range un objet. Cette fin-là est celle de le toboggan, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8484,6 +8530,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8655,6 +8702,7 @@
           <t>narrateur|Léa a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8850,6 +8898,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9021,6 +9070,7 @@
           <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9188,6 +9238,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9359,6 +9410,7 @@
           <t>narrateur|Léa rejoint Léa. La couverture est douce. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9526,6 +9578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9697,6 +9750,7 @@
           <t>narrateur|Léa rejoint Sami. On entend un oiseau. On range un objet. Cette fin-là est celle de le toboggan, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9864,6 +9918,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10035,6 +10090,7 @@
           <t>narrateur|Léa a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10230,6 +10286,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10401,6 +10458,7 @@
           <t>narrateur|Léa rejoint Tom. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10568,6 +10626,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10739,6 +10798,7 @@
           <t>narrateur|Léa rejoint Léa. On entend un oiseau. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10906,6 +10966,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11077,6 +11138,7 @@
           <t>narrateur|Léa rejoint Sami. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le toboggan, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11244,6 +11306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11416,6 +11479,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11603,6 +11667,7 @@
           <t>narrateur|Que fait-on ? Les prises sont pour les adultes.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11778,6 +11843,7 @@
           <t>narrateur|Oui. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa respire. Léa retient : appeler un adulte, mains avec les jouets. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11969,6 +12035,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12140,6 +12207,7 @@
           <t>narrateur|Léa a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12335,6 +12403,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12506,6 +12575,7 @@
           <t>narrateur|Léa rejoint Tom. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12673,6 +12743,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12844,6 +12915,7 @@
           <t>narrateur|Léa rejoint Léa. La couverture est douce. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13011,6 +13083,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13182,6 +13255,7 @@
           <t>narrateur|Léa rejoint Sami. On entend un oiseau. On dit merci. Cette fin-là est celle de les balançoires, le ballon et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13349,6 +13423,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13520,6 +13595,7 @@
           <t>narrateur|Léa a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13715,6 +13791,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13886,6 +13963,7 @@
           <t>narrateur|Léa rejoint Tom. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14053,6 +14131,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14224,6 +14303,7 @@
           <t>narrateur|Léa rejoint Léa. On entend un oiseau. On range un objet. Cette fin-là est celle de les balançoires, le seau et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14391,6 +14471,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14562,6 +14643,7 @@
           <t>narrateur|Léa rejoint Sami. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de les balançoires, le seau et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14729,6 +14811,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14900,6 +14983,7 @@
           <t>narrateur|Léa a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa répète tout bas : appeler un adulte, mains avec les jouets. On souffle doucement. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15095,6 +15179,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15266,6 +15351,7 @@
           <t>narrateur|Léa rejoint Tom. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Tom. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15433,6 +15519,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15604,6 +15691,7 @@
           <t>narrateur|Léa rejoint Léa. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Léa. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15771,6 +15859,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15942,6 +16031,7 @@
           <t>narrateur|Léa rejoint Sami. Le vent est doux. On dit merci. Cette fin-là est celle de les balançoires, le doudou et Sami. Léa a appris : Les prises sont pour les adultes. Voici le geste : appeler papa ou maman ; garder les mains avec les jouets. Léa a entendu : appeler un adulte, mains avec les jouets. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16109,6 +16199,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16127,7 +16218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16207,6 +16298,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16221,7 +16326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16408,6 +16513,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
